--- a/data-raw/metadata/feather_metadata.xlsx
+++ b/data-raw/metadata/feather_metadata.xlsx
@@ -1039,7 +1039,7 @@
         <v>35786</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46149</v>
+        <v>46178</v>
       </c>
     </row>
   </sheetData>
